--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         <v>46119.59377314815</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46238.34243055555</v>
+        <v>46243.76255787037</v>
       </c>
       <c r="R10" t="n">
-        <v>49.6</v>
+        <v>54.5</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -7380,10 +7380,10 @@
         <v>46181.45489583333</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46181.47431712963</v>
+        <v>46243.76255787037</v>
       </c>
       <c r="R67" t="n">
-        <v>26</v>
+        <v>31.9</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -13061,10 +13061,10 @@
         <v>46114.48128472222</v>
       </c>
       <c r="Q122" s="1" t="n">
-        <v>46240.65493055555</v>
+        <v>46243.76325231481</v>
       </c>
       <c r="R122" t="n">
-        <v>40.3</v>
+        <v>46.3</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -23674,26 +23674,26 @@
         </is>
       </c>
       <c r="M225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Other, Spearmint</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P225" s="1" t="n">
         <v>46196.58053240741</v>
       </c>
       <c r="Q225" s="1" t="n">
-        <v>46196.58053240741</v>
+        <v>46242.89173611111</v>
       </c>
       <c r="R225" t="n">
-        <v>6</v>
+        <v>10.9</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -4724,7 +4724,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -18887,7 +18887,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -20432,7 +20432,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -20840,7 +20840,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -21458,7 +21458,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -22591,7 +22591,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -25031,7 +25031,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -25134,7 +25134,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -25760,7 +25760,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -26588,7 +26588,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -27931,7 +27931,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -28034,7 +28034,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -28141,7 +28141,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -28347,7 +28347,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -28763,7 +28763,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -30827,7 +30827,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -31136,7 +31136,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -31651,7 +31651,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -31754,7 +31754,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -31857,7 +31857,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -32067,7 +32067,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -32376,7 +32376,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -32586,7 +32586,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -32689,7 +32689,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -33513,7 +33513,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -34028,7 +34028,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -35062,7 +35062,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -35165,7 +35165,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -35478,7 +35478,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -35581,7 +35581,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -35890,7 +35890,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -35993,7 +35993,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -36821,7 +36821,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -37851,7 +37851,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -38366,7 +38366,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -38885,7 +38885,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -38988,7 +38988,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -39297,7 +39297,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -39400,7 +39400,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -39919,7 +39919,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -40232,7 +40232,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -40747,7 +40747,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -40957,7 +40957,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -41266,7 +41266,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -41472,7 +41472,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -41682,7 +41682,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -42922,7 +42922,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -43025,7 +43025,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -43231,7 +43231,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -43746,7 +43746,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -43952,7 +43952,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -44364,7 +44364,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -45489,7 +45489,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -45798,7 +45798,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -45901,7 +45901,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -46004,7 +46004,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -46210,7 +46210,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -46313,7 +46313,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -46622,7 +46622,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -46828,7 +46828,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -46931,7 +46931,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -47034,7 +47034,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -47343,7 +47343,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -47652,7 +47652,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -47961,7 +47961,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -48064,7 +48064,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -48270,7 +48270,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -48484,7 +48484,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -48587,7 +48587,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -49102,7 +49102,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -49308,7 +49308,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -49411,7 +49411,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -49617,7 +49617,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -49926,7 +49926,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -50029,7 +50029,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -50235,7 +50235,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -50441,7 +50441,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -50548,7 +50548,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -50857,7 +50857,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -50960,7 +50960,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -51372,7 +51372,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -51475,7 +51475,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -51990,7 +51990,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -52093,7 +52093,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -52715,7 +52715,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -52818,7 +52818,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -53230,7 +53230,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -53333,7 +53333,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -53436,7 +53436,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -53539,7 +53539,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -53642,7 +53642,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -54058,7 +54058,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -54264,7 +54264,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -54676,7 +54676,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -54779,7 +54779,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -55052,7 +55052,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -55155,7 +55155,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -55258,7 +55258,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -55361,7 +55361,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -55464,7 +55464,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -55773,7 +55773,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -55983,7 +55983,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -56090,7 +56090,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -56399,7 +56399,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -57635,7 +57635,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -57738,7 +57738,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -57944,7 +57944,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -58150,7 +58150,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -58459,7 +58459,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -58562,7 +58562,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -58665,7 +58665,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -58768,7 +58768,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -58974,7 +58974,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -59077,7 +59077,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -59180,7 +59180,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -59283,7 +59283,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -59493,7 +59493,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -59699,7 +59699,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -60111,7 +60111,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -60214,7 +60214,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -61672,7 +61672,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -63015,7 +63015,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -63118,7 +63118,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -63530,7 +63530,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -63736,7 +63736,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -63839,7 +63839,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -64873,7 +64873,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -65285,7 +65285,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -65491,7 +65491,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -65800,7 +65800,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -65907,7 +65907,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -66117,7 +66117,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -66220,7 +66220,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -66945,7 +66945,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -67357,7 +67357,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -67563,7 +67563,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -67666,7 +67666,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -68078,7 +68078,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -68490,7 +68490,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -68906,7 +68906,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -69215,7 +69215,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -69322,7 +69322,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -69425,7 +69425,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -70047,7 +70047,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -70150,7 +70150,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -70356,7 +70356,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -70665,7 +70665,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -70768,7 +70768,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -71081,7 +71081,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -71390,7 +71390,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -71493,7 +71493,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -71596,7 +71596,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -72115,7 +72115,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -72218,7 +72218,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -72939,7 +72939,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -73145,7 +73145,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -73454,7 +73454,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -73660,7 +73660,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -73866,7 +73866,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -74175,7 +74175,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -74484,7 +74484,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -74690,7 +74690,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -75205,7 +75205,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -75308,7 +75308,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -75617,7 +75617,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -75823,7 +75823,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -75926,7 +75926,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -76029,7 +76029,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -76235,7 +76235,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -76647,7 +76647,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -76750,7 +76750,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -76956,7 +76956,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -77059,7 +77059,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -77162,7 +77162,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -77471,7 +77471,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -77574,7 +77574,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -77677,7 +77677,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -78089,7 +78089,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -78196,7 +78196,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -78711,7 +78711,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -78814,7 +78814,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -78917,7 +78917,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -79020,7 +79020,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
@@ -79499,7 +79499,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -79606,7 +79606,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -79812,7 +79812,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -80121,7 +80121,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -80224,7 +80224,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -80430,7 +80430,7 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -80640,7 +80640,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -81262,7 +81262,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -81571,7 +81571,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -81674,7 +81674,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -81777,7 +81777,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -81983,7 +81983,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -82189,7 +82189,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -82918,7 +82918,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -83021,7 +83021,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -83124,7 +83124,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -83330,7 +83330,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -83639,7 +83639,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -84051,7 +84051,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -84154,7 +84154,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -84669,7 +84669,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -85081,7 +85081,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -85390,7 +85390,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -85596,7 +85596,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -85699,7 +85699,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -86008,7 +86008,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -86111,7 +86111,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -86214,7 +86214,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -86523,7 +86523,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -86729,7 +86729,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -87141,7 +87141,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -87244,7 +87244,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -87664,7 +87664,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -88179,7 +88179,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -88286,7 +88286,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -88492,7 +88492,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -88595,7 +88595,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -88698,7 +88698,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -89217,7 +89217,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -89736,7 +89736,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -90148,7 +90148,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -3727,11 +3727,11 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee, Green Burner, Other, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3743,10 +3743,10 @@
         <v>46069.32224537037</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46169.4778125</v>
+        <v>46251.49799768518</v>
       </c>
       <c r="R32" t="n">
-        <v>18.4</v>
+        <v>24.4</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -15386,11 +15386,11 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Ashwagandha, Ashwagandha Coffee, Green Burner, Hibiscus, Spearmint, Turmeric Curcumin</t>
+          <t>Ashwagandha, Ashwagandha Coffee, Green Burner, Hibiscus, Other, Spearmint, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -15402,7 +15402,7 @@
         <v>46156.56252314815</v>
       </c>
       <c r="Q145" s="1" t="n">
-        <v>46210.57987268519</v>
+        <v>46251.93547453704</v>
       </c>
       <c r="R145" t="n">
         <v>51.7</v>
@@ -39405,7 +39405,7 @@
         </is>
       </c>
       <c r="M378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N378" t="inlineStr">
         <is>
@@ -39414,17 +39414,17 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P378" s="1" t="n">
         <v>46126.51599537037</v>
       </c>
       <c r="Q378" s="1" t="n">
-        <v>46192.55383101852</v>
+        <v>46251.71811342592</v>
       </c>
       <c r="R378" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -45700,11 +45700,11 @@
         </is>
       </c>
       <c r="M439" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee, Other, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -45716,7 +45716,7 @@
         <v>46176.5909837963</v>
       </c>
       <c r="Q439" s="1" t="n">
-        <v>46202.31462962963</v>
+        <v>46251.47366898148</v>
       </c>
       <c r="R439" t="n">
         <v>12.5</v>
@@ -47966,11 +47966,11 @@
         </is>
       </c>
       <c r="M461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Other</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -47982,7 +47982,7 @@
         <v>46203.53618055556</v>
       </c>
       <c r="Q461" s="1" t="n">
-        <v>46203.53618055556</v>
+        <v>46251.88269675926</v>
       </c>
       <c r="R461" t="n">
         <v>6</v>
@@ -60120,26 +60120,26 @@
         </is>
       </c>
       <c r="M579" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N579" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Green Burner, Other, Spearmint</t>
         </is>
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P579" s="1" t="n">
         <v>46250.53894675926</v>
       </c>
       <c r="Q579" s="1" t="n">
-        <v>46250.53894675926</v>
+        <v>46251.90909722223</v>
       </c>
       <c r="R579" t="n">
-        <v>6</v>
+        <v>16.8</v>
       </c>
       <c r="S579" t="inlineStr">
         <is>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -695,7 +695,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>0.38</t>
@@ -1218,7 +1222,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>0.32</t>
@@ -1424,7 +1432,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -1527,7 +1539,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>0.37</t>
@@ -2050,7 +2066,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>0.56</t>
@@ -2153,7 +2173,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>1.25</t>
@@ -2466,7 +2490,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>0.74</t>
@@ -2672,7 +2700,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>0.53</t>
@@ -2775,7 +2807,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -2878,7 +2914,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>0.95</t>
@@ -2981,7 +3021,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>0.23</t>
@@ -3084,7 +3128,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>0.71</t>
@@ -3187,7 +3235,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>1.43</t>
@@ -3603,7 +3655,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>0.53</t>
@@ -3916,7 +3972,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>0.86</t>
@@ -4019,7 +4079,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>0.51</t>
@@ -4229,7 +4293,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>1.04</t>
@@ -4332,7 +4400,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>0.46</t>
@@ -4435,7 +4507,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>0.91</t>
@@ -4645,7 +4721,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>0.98</t>
@@ -4855,7 +4935,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>0.99</t>
@@ -5061,7 +5145,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>0.95</t>
@@ -5164,7 +5252,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>0.52</t>
@@ -5477,7 +5569,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>0.83</t>
@@ -5582,7 +5678,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5687,7 +5783,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>0.92</t>
@@ -5790,7 +5890,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>1.92</t>
@@ -6103,7 +6207,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -6313,7 +6421,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>0.27</t>
@@ -6523,7 +6635,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>0.93</t>
@@ -6729,7 +6845,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -6832,7 +6952,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>0.91</t>
@@ -7038,7 +7162,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>0.99</t>
@@ -7141,7 +7269,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>1.03</t>
@@ -7347,7 +7479,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>1.15</t>
@@ -7553,7 +7689,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>0.6</t>
@@ -7866,7 +8006,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>1.17</t>
@@ -7969,7 +8113,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>1.31</t>
@@ -8072,7 +8220,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>0.69</t>
@@ -8278,7 +8430,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>0.14</t>
@@ -8381,7 +8537,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>0.6</t>
@@ -8484,7 +8644,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>0.81</t>
@@ -8793,7 +8957,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>0.21</t>
@@ -9205,7 +9373,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>1</t>
@@ -9411,7 +9583,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>0.58</t>
@@ -9514,7 +9690,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>0.8</t>
@@ -9823,7 +10003,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>0.82</t>
@@ -10239,7 +10423,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>0.88</t>
@@ -10758,7 +10946,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -10964,7 +11156,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>0.57</t>
@@ -11067,7 +11263,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -11170,7 +11370,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -11273,7 +11477,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>1</t>
@@ -11352,7 +11560,11 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
@@ -11443,7 +11655,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>1.32</t>
@@ -11653,7 +11869,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -11756,7 +11976,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>0.63</t>
@@ -12168,7 +12392,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>1.22</t>
@@ -12374,7 +12602,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>0.75</t>
@@ -12477,7 +12709,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>0.99</t>
@@ -12580,7 +12816,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>0.17</t>
@@ -12683,7 +12923,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>0.19</t>
@@ -12786,7 +13030,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>0.75</t>
@@ -12889,7 +13137,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>0.68</t>
@@ -12992,7 +13244,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -13095,7 +13351,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -13301,7 +13561,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -13404,7 +13668,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>3.64</t>
@@ -13610,7 +13878,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>1.26</t>
@@ -13713,7 +13985,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>0.86</t>
@@ -13816,7 +14092,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -13919,7 +14199,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>1.37</t>
@@ -14022,7 +14306,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>2.37</t>
@@ -14228,7 +14516,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
           <t>0.81</t>
@@ -14331,7 +14623,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>0.96</t>
@@ -14541,7 +14837,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>0.44</t>
@@ -14644,7 +14944,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>0.22</t>
@@ -14747,7 +15051,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>0.22</t>
@@ -14850,7 +15158,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>0.93</t>
@@ -15056,7 +15368,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>0.53</t>
@@ -15159,7 +15475,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr">
         <is>
           <t>1.04</t>
@@ -15262,7 +15582,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -15365,7 +15689,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>0.78</t>
@@ -15674,7 +16002,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr">
         <is>
           <t>0.59</t>
@@ -15880,7 +16212,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>0.65</t>
@@ -16086,7 +16422,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -16292,7 +16632,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>1.28</t>
@@ -16395,7 +16739,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>0.75</t>
@@ -16605,7 +16953,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
           <t>0.39</t>
@@ -16708,7 +17060,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr">
         <is>
           <t>3.57</t>
@@ -16811,7 +17167,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr">
         <is>
           <t>1.74</t>
@@ -16914,7 +17274,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr">
         <is>
           <t>2.08</t>
@@ -17120,7 +17484,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr">
         <is>
           <t>3.07</t>
@@ -17223,7 +17591,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J163" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -17326,7 +17698,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>2.95</t>
@@ -17429,7 +17805,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J165" t="inlineStr">
         <is>
           <t>0.69</t>
@@ -17532,7 +17912,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr">
         <is>
           <t>1.26</t>
@@ -17841,7 +18225,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr">
         <is>
           <t>0.6</t>
@@ -17944,7 +18332,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -18150,7 +18542,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -18566,7 +18962,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr">
         <is>
           <t>1</t>
@@ -18879,7 +19279,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>0.9</t>
@@ -18982,7 +19386,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J180" t="inlineStr">
         <is>
           <t>1.64</t>
@@ -19188,7 +19596,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr">
         <is>
           <t>0.9</t>
@@ -19291,7 +19703,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -19394,7 +19810,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J184" t="inlineStr">
         <is>
           <t>0.98</t>
@@ -19497,7 +19917,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>0.75</t>
@@ -19600,7 +20024,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr">
         <is>
           <t>0.71</t>
@@ -19703,7 +20131,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J187" t="inlineStr">
         <is>
           <t>0.52</t>
@@ -19806,7 +20238,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J188" t="inlineStr">
         <is>
           <t>0.8</t>
@@ -19909,7 +20345,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>1.63</t>
@@ -20012,7 +20452,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J190" t="inlineStr">
         <is>
           <t>0.67</t>
@@ -20218,7 +20662,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr">
         <is>
           <t>1.14</t>
@@ -20420,7 +20868,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J194" t="inlineStr">
         <is>
           <t>0.39</t>
@@ -21141,7 +21593,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr">
         <is>
           <t>0.62</t>
@@ -21244,7 +21700,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr">
         <is>
           <t>0.9</t>
@@ -21450,7 +21910,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J204" t="inlineStr">
         <is>
           <t>1.71</t>
@@ -21656,7 +22120,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J206" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -21862,7 +22330,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J208" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -21965,7 +22437,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J209" t="inlineStr">
         <is>
           <t>0.9</t>
@@ -22171,7 +22647,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
           <t>0.26</t>
@@ -22274,7 +22754,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr">
         <is>
           <t>1.31</t>
@@ -22377,7 +22861,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J213" t="inlineStr">
         <is>
           <t>0.61</t>
@@ -22480,7 +22968,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J214" t="inlineStr">
         <is>
           <t>0.52</t>
@@ -23102,7 +23594,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J220" t="inlineStr">
         <is>
           <t>0.82</t>
@@ -23205,7 +23701,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
       <c r="J221" t="inlineStr">
         <is>
           <t>0.37</t>
@@ -23308,7 +23808,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J222" t="inlineStr">
         <is>
           <t>0.95</t>
@@ -23411,7 +23915,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J223" t="inlineStr">
         <is>
           <t>1.81</t>
@@ -23617,7 +24125,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J225" t="inlineStr">
         <is>
           <t>0.81</t>
@@ -23720,7 +24232,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J226" t="inlineStr">
         <is>
           <t>0.97</t>
@@ -23823,7 +24339,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J227" t="inlineStr">
         <is>
           <t>0.97</t>
@@ -24009,7 +24529,11 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
@@ -24199,7 +24723,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J231" t="inlineStr">
         <is>
           <t>0.2</t>
@@ -24405,7 +24933,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J233" t="inlineStr">
         <is>
           <t>1.12</t>
@@ -24508,7 +25040,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J234" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -24611,7 +25147,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J235" t="inlineStr">
         <is>
           <t>9.24</t>
@@ -24817,7 +25357,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J237" t="inlineStr">
         <is>
           <t>1.34</t>
@@ -25332,7 +25876,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J242" t="inlineStr">
         <is>
           <t>1.65</t>
@@ -25437,7 +25985,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -25649,7 +26197,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J245" t="inlineStr">
         <is>
           <t>3.14</t>
@@ -25752,7 +26304,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
           <t>3.02</t>
@@ -25962,7 +26518,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J248" t="inlineStr">
         <is>
           <t>0.66</t>
@@ -26065,7 +26625,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J249" t="inlineStr">
         <is>
           <t>0.77</t>
@@ -26271,7 +26835,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J251" t="inlineStr">
         <is>
           <t>0.53</t>
@@ -26374,7 +26942,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J252" t="inlineStr">
         <is>
           <t>8.57</t>
@@ -26477,7 +27049,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J253" t="inlineStr">
         <is>
           <t>0.47</t>
@@ -26790,7 +27366,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J256" t="inlineStr">
         <is>
           <t>0.78</t>
@@ -26893,7 +27473,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J257" t="inlineStr">
         <is>
           <t>0.55</t>
@@ -26996,7 +27580,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J258" t="inlineStr">
         <is>
           <t>1.4</t>
@@ -27202,7 +27790,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J260" t="inlineStr">
         <is>
           <t>0.46</t>
@@ -27408,7 +28000,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J262" t="inlineStr">
         <is>
           <t>1.06</t>
@@ -27511,7 +28107,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J263" t="inlineStr">
         <is>
           <t>0.76</t>
@@ -27614,7 +28214,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J264" t="inlineStr">
         <is>
           <t>1.54</t>
@@ -28030,7 +28634,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J268" t="inlineStr">
         <is>
           <t>0.88</t>
@@ -28343,7 +28951,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J271" t="inlineStr">
         <is>
           <t>0.94</t>
@@ -28446,7 +29058,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J272" t="inlineStr">
         <is>
           <t>0.71</t>
@@ -28549,7 +29165,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J273" t="inlineStr">
         <is>
           <t>0.46</t>
@@ -28652,7 +29272,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J274" t="inlineStr">
         <is>
           <t>1.15</t>
@@ -28755,7 +29379,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J275" t="inlineStr">
         <is>
           <t>0.65</t>
@@ -28961,7 +29589,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J277" t="inlineStr">
         <is>
           <t>0.75</t>
@@ -29064,7 +29696,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr">
         <is>
           <t>0.98</t>
@@ -29169,7 +29805,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -29377,7 +30013,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr">
         <is>
           <t>0.67</t>
@@ -29480,7 +30120,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J282" t="inlineStr">
         <is>
           <t>1.29</t>
@@ -29583,7 +30227,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
       <c r="J283" t="inlineStr">
         <is>
           <t>0.76</t>
@@ -30201,7 +30849,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J289" t="inlineStr">
         <is>
           <t>4.86</t>
@@ -30510,7 +31162,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J292" t="inlineStr">
         <is>
           <t>0.78</t>
@@ -30716,7 +31372,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J294" t="inlineStr">
         <is>
           <t>0.76</t>
@@ -30819,7 +31479,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J295" t="inlineStr">
         <is>
           <t>16.91</t>
@@ -30922,7 +31586,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J296" t="inlineStr">
         <is>
           <t>2.15</t>
@@ -31025,7 +31693,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J297" t="inlineStr">
         <is>
           <t>0.64</t>
@@ -31128,7 +31800,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J298" t="inlineStr">
         <is>
           <t>0.31</t>
@@ -31334,7 +32010,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J300" t="inlineStr">
         <is>
           <t>0.92</t>
@@ -31540,7 +32220,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J302" t="inlineStr">
         <is>
           <t>1.89</t>
@@ -31849,7 +32533,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J305" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -31954,7 +32642,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -32059,7 +32747,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J307" t="inlineStr">
         <is>
           <t>0.76</t>
@@ -32364,7 +33056,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J310" t="inlineStr">
         <is>
           <t>1.23</t>
@@ -32776,7 +33472,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J314" t="inlineStr">
         <is>
           <t>0.62</t>
@@ -32879,7 +33579,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J315" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -32982,7 +33686,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J316" t="inlineStr">
         <is>
           <t>1.3</t>
@@ -33295,7 +34003,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J319" t="inlineStr">
         <is>
           <t>1.02</t>
@@ -33398,7 +34110,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J320" t="inlineStr">
         <is>
           <t>0.32</t>
@@ -33501,7 +34217,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J321" t="inlineStr">
         <is>
           <t>1.32</t>
@@ -33604,7 +34324,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J322" t="inlineStr">
         <is>
           <t>0.41</t>
@@ -33707,7 +34431,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J323" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -34119,7 +34847,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J327" t="inlineStr">
         <is>
           <t>0.63</t>
@@ -34222,7 +34954,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J328" t="inlineStr">
         <is>
           <t>1.22</t>
@@ -34325,7 +35061,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J329" t="inlineStr">
         <is>
           <t>0.52</t>
@@ -34428,7 +35168,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J330" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -34531,7 +35275,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J331" t="inlineStr">
         <is>
           <t>0.64</t>
@@ -34634,7 +35382,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J332" t="inlineStr">
         <is>
           <t>1.57</t>
@@ -34816,7 +35568,11 @@
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr"/>
@@ -35014,7 +35770,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J336" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -35117,7 +35877,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J337" t="inlineStr">
         <is>
           <t>0.96</t>
@@ -35636,7 +36400,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J342" t="inlineStr">
         <is>
           <t>4.13</t>
@@ -35739,7 +36507,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J343" t="inlineStr">
         <is>
           <t>2.56</t>
@@ -35842,7 +36614,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J344" t="inlineStr">
         <is>
           <t>0.69</t>
@@ -35945,7 +36721,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J345" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -36155,7 +36935,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J347" t="inlineStr">
         <is>
           <t>0.47</t>
@@ -36258,7 +37042,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J348" t="inlineStr">
         <is>
           <t>0.96</t>
@@ -36361,7 +37149,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J349" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -36567,7 +37359,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr"/>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J351" t="inlineStr">
         <is>
           <t>0.15</t>
@@ -36670,7 +37466,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr"/>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J352" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -36773,7 +37573,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr"/>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J353" t="inlineStr">
         <is>
           <t>0.33</t>
@@ -36876,7 +37680,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I354" t="inlineStr"/>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J354" t="inlineStr">
         <is>
           <t>0.53</t>
@@ -36979,7 +37787,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr"/>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J355" t="inlineStr">
         <is>
           <t>0.99</t>
@@ -37185,7 +37997,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr"/>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J357" t="inlineStr">
         <is>
           <t>0.69</t>
@@ -37288,7 +38104,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr"/>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J358" t="inlineStr">
         <is>
           <t>0.82</t>
@@ -37391,7 +38211,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J359" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -37494,7 +38318,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr"/>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J360" t="inlineStr">
         <is>
           <t>1.09</t>
@@ -37700,7 +38528,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr"/>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J362" t="inlineStr">
         <is>
           <t>0.86</t>
@@ -37803,7 +38635,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I363" t="inlineStr"/>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J363" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -38112,7 +38948,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I366" t="inlineStr"/>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J366" t="inlineStr">
         <is>
           <t>0.74</t>
@@ -38215,7 +39055,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I367" t="inlineStr"/>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J367" t="inlineStr">
         <is>
           <t>0.83</t>
@@ -38318,7 +39162,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr"/>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J368" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -38421,7 +39269,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr"/>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J369" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -38627,7 +39479,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr"/>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J371" t="inlineStr">
         <is>
           <t>1</t>
@@ -38936,7 +39792,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr"/>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J374" t="inlineStr">
         <is>
           <t>0.35</t>
@@ -39039,7 +39899,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr"/>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J375" t="inlineStr">
         <is>
           <t>0.14</t>
@@ -39142,7 +40006,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr"/>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J376" t="inlineStr">
         <is>
           <t>0.52</t>
@@ -39245,7 +40113,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr"/>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J377" t="inlineStr">
         <is>
           <t>0.42</t>
@@ -39348,7 +40220,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr"/>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J378" t="inlineStr">
         <is>
           <t>1.9</t>
@@ -39556,7 +40432,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -39867,7 +40743,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I383" t="inlineStr"/>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J383" t="inlineStr">
         <is>
           <t>0.86</t>
@@ -39970,7 +40850,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I384" t="inlineStr"/>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J384" t="inlineStr">
         <is>
           <t>1.19</t>
@@ -40073,7 +40957,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr"/>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J385" t="inlineStr">
         <is>
           <t>2.19</t>
@@ -40176,7 +41064,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I386" t="inlineStr"/>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J386" t="inlineStr">
         <is>
           <t>1.07</t>
@@ -40386,7 +41278,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr"/>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J388" t="inlineStr">
         <is>
           <t>0.99</t>
@@ -40592,7 +41488,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr"/>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J390" t="inlineStr">
         <is>
           <t>0.42</t>
@@ -40802,7 +41702,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I392" t="inlineStr"/>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J392" t="inlineStr">
         <is>
           <t>0.95</t>
@@ -40905,7 +41809,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I393" t="inlineStr"/>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J393" t="inlineStr">
         <is>
           <t>0.76</t>
@@ -41111,7 +42019,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I395" t="inlineStr"/>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J395" t="inlineStr">
         <is>
           <t>0.57</t>
@@ -41317,7 +42229,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr"/>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J397" t="inlineStr">
         <is>
           <t>0.96</t>
@@ -41630,7 +42546,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I400" t="inlineStr"/>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J400" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -41840,7 +42760,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J402" t="inlineStr">
         <is>
           <t>1.01</t>
@@ -42046,7 +42970,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I404" t="inlineStr"/>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J404" t="inlineStr">
         <is>
           <t>1.51</t>
@@ -42252,7 +43180,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I406" t="inlineStr"/>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J406" t="inlineStr">
         <is>
           <t>4.36</t>
@@ -42355,7 +43287,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I407" t="inlineStr"/>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J407" t="inlineStr">
         <is>
           <t>0.88</t>
@@ -42458,7 +43394,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I408" t="inlineStr"/>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J408" t="inlineStr">
         <is>
           <t>1.82</t>
@@ -42561,7 +43501,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I409" t="inlineStr"/>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J409" t="inlineStr">
         <is>
           <t>0.79</t>
@@ -42664,7 +43608,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I410" t="inlineStr"/>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J410" t="inlineStr">
         <is>
           <t>0.62</t>
@@ -42767,7 +43715,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I411" t="inlineStr"/>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J411" t="inlineStr">
         <is>
           <t>0.96</t>
@@ -42973,7 +43925,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I413" t="inlineStr"/>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J413" t="inlineStr">
         <is>
           <t>1.06</t>
@@ -43076,7 +44032,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I414" t="inlineStr"/>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J414" t="inlineStr">
         <is>
           <t>0.48</t>
@@ -43179,7 +44139,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J415" t="inlineStr">
         <is>
           <t>0.84</t>
@@ -43282,7 +44246,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I416" t="inlineStr"/>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J416" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -43797,7 +44765,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I421" t="inlineStr"/>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J421" t="inlineStr">
         <is>
           <t>0.58</t>
@@ -43900,7 +44872,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I422" t="inlineStr"/>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J422" t="inlineStr">
         <is>
           <t>3.03</t>
@@ -44003,7 +44979,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I423" t="inlineStr"/>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J423" t="inlineStr">
         <is>
           <t>0.79</t>
@@ -44106,7 +45086,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I424" t="inlineStr"/>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J424" t="inlineStr">
         <is>
           <t>0.63</t>
@@ -44209,7 +45193,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I425" t="inlineStr"/>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J425" t="inlineStr">
         <is>
           <t>0.37</t>
@@ -44312,7 +45300,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I426" t="inlineStr"/>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J426" t="inlineStr">
         <is>
           <t>0.75</t>
@@ -44415,7 +45407,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I427" t="inlineStr"/>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J427" t="inlineStr">
         <is>
           <t>0</t>
@@ -44621,7 +45617,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I429" t="inlineStr"/>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J429" t="inlineStr">
         <is>
           <t>0.44</t>
@@ -45033,7 +46033,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I433" t="inlineStr"/>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J433" t="inlineStr">
         <is>
           <t>0.16</t>
@@ -45342,7 +46346,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I436" t="inlineStr"/>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J436" t="inlineStr">
         <is>
           <t>0.41</t>
@@ -45445,7 +46453,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I437" t="inlineStr"/>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J437" t="inlineStr">
         <is>
           <t>2.82</t>
@@ -45548,7 +46560,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I438" t="inlineStr"/>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J438" t="inlineStr">
         <is>
           <t>1</t>
@@ -45857,7 +46873,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I441" t="inlineStr"/>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J441" t="inlineStr">
         <is>
           <t>4.82</t>
@@ -46273,7 +47293,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I445" t="inlineStr"/>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J445" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -46479,7 +47503,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I447" t="inlineStr"/>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J447" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -46788,7 +47816,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I450" t="inlineStr"/>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J450" t="inlineStr">
         <is>
           <t>0.18</t>
@@ -46994,7 +48026,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I452" t="inlineStr"/>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J452" t="inlineStr">
         <is>
           <t>2.23</t>
@@ -47200,7 +48236,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I454" t="inlineStr"/>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J454" t="inlineStr">
         <is>
           <t>0.23</t>
@@ -47303,7 +48343,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I455" t="inlineStr"/>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J455" t="inlineStr">
         <is>
           <t>3.06</t>
@@ -47406,7 +48450,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I456" t="inlineStr"/>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J456" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -47822,7 +48870,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I460" t="inlineStr"/>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J460" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -47925,7 +48977,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I461" t="inlineStr"/>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J461" t="inlineStr">
         <is>
           <t>1.23</t>
@@ -48028,7 +49084,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I462" t="inlineStr"/>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J462" t="inlineStr">
         <is>
           <t>0.57</t>
@@ -48131,7 +49191,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I463" t="inlineStr"/>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J463" t="inlineStr">
         <is>
           <t>1.06</t>
@@ -48337,7 +49401,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I465" t="inlineStr"/>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J465" t="inlineStr">
         <is>
           <t>0.25</t>
@@ -49276,7 +50344,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I474" t="inlineStr"/>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J474" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -49482,7 +50554,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr"/>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J476" t="inlineStr">
         <is>
           <t>1.8</t>
@@ -49585,7 +50661,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I477" t="inlineStr"/>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J477" t="inlineStr">
         <is>
           <t>0.63</t>
@@ -49688,7 +50768,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I478" t="inlineStr"/>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J478" t="inlineStr">
         <is>
           <t>1.65</t>
@@ -49791,7 +50875,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I479" t="inlineStr"/>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J479" t="inlineStr">
         <is>
           <t>1.24</t>
@@ -49894,7 +50982,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I480" t="inlineStr"/>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J480" t="inlineStr">
         <is>
           <t>0.8</t>
@@ -49997,7 +51089,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I481" t="inlineStr"/>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J481" t="inlineStr">
         <is>
           <t>1.31</t>
@@ -50100,7 +51196,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I482" t="inlineStr"/>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J482" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -50409,7 +51509,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I485" t="inlineStr"/>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J485" t="inlineStr">
         <is>
           <t>1.78</t>
@@ -50512,7 +51616,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I486" t="inlineStr"/>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J486" t="inlineStr">
         <is>
           <t>0.97</t>
@@ -50615,7 +51723,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I487" t="inlineStr"/>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J487" t="inlineStr">
         <is>
           <t>0.57</t>
@@ -50718,7 +51830,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I488" t="inlineStr"/>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J488" t="inlineStr">
         <is>
           <t>1.08</t>
@@ -50821,7 +51937,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I489" t="inlineStr"/>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J489" t="inlineStr">
         <is>
           <t>0.44</t>
@@ -51237,7 +52357,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I493" t="inlineStr"/>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J493" t="inlineStr">
         <is>
           <t>1.08</t>
@@ -51340,7 +52464,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I494" t="inlineStr"/>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J494" t="inlineStr">
         <is>
           <t>0.97</t>
@@ -51443,7 +52571,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I495" t="inlineStr"/>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J495" t="inlineStr">
         <is>
           <t>1.03</t>
@@ -51752,7 +52884,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I498" t="inlineStr"/>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J498" t="inlineStr">
         <is>
           <t>1.57</t>
@@ -51855,7 +52991,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I499" t="inlineStr"/>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J499" t="inlineStr">
         <is>
           <t>0.92</t>
@@ -51958,7 +53098,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I500" t="inlineStr"/>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J500" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -52061,7 +53205,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I501" t="inlineStr"/>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J501" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -52370,7 +53518,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I504" t="inlineStr"/>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J504" t="inlineStr">
         <is>
           <t>0.94</t>
@@ -52475,7 +53627,7 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
@@ -52580,7 +53732,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I506" t="inlineStr"/>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J506" t="inlineStr">
         <is>
           <t>1.04</t>
@@ -52683,7 +53839,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I507" t="inlineStr"/>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J507" t="inlineStr">
         <is>
           <t>1.01</t>
@@ -52786,7 +53946,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I508" t="inlineStr"/>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J508" t="inlineStr">
         <is>
           <t>0.74</t>
@@ -52889,7 +54053,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I509" t="inlineStr"/>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J509" t="inlineStr">
         <is>
           <t>1.83</t>
@@ -52992,7 +54160,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I510" t="inlineStr"/>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J510" t="inlineStr">
         <is>
           <t>0.67</t>
@@ -53095,7 +54267,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I511" t="inlineStr"/>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J511" t="inlineStr">
         <is>
           <t>1.6</t>
@@ -53198,7 +54374,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I512" t="inlineStr"/>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J512" t="inlineStr">
         <is>
           <t>0.65</t>
@@ -53301,7 +54481,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I513" t="inlineStr"/>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J513" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -53404,7 +54588,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I514" t="inlineStr"/>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J514" t="inlineStr">
         <is>
           <t>3.62</t>
@@ -53507,7 +54695,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I515" t="inlineStr"/>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J515" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -53820,7 +55012,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I518" t="inlineStr"/>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J518" t="inlineStr">
         <is>
           <t>1.04</t>
@@ -54026,7 +55222,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I520" t="inlineStr"/>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J520" t="inlineStr">
         <is>
           <t>0.81</t>
@@ -54129,7 +55329,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I521" t="inlineStr"/>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J521" t="inlineStr">
         <is>
           <t>0.38</t>
@@ -54339,7 +55543,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I523" t="inlineStr"/>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J523" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -54442,7 +55650,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr"/>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J524" t="inlineStr">
         <is>
           <t>0.54</t>
@@ -54545,7 +55757,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I525" t="inlineStr"/>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J525" t="inlineStr">
         <is>
           <t>1.5</t>
@@ -54957,7 +56173,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I529" t="inlineStr"/>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J529" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -55163,7 +56383,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I531" t="inlineStr"/>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J531" t="inlineStr">
         <is>
           <t>1.01</t>
@@ -55369,7 +56593,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I533" t="inlineStr"/>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J533" t="inlineStr">
         <is>
           <t>0.64</t>
@@ -55781,7 +57009,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I537" t="inlineStr"/>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J537" t="inlineStr">
         <is>
           <t>2.31</t>
@@ -55991,7 +57223,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I539" t="inlineStr"/>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J539" t="inlineStr">
         <is>
           <t>2.91</t>
@@ -56070,7 +57306,11 @@
       <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr"/>
-      <c r="I540" t="inlineStr"/>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr"/>
       <c r="L540" t="inlineStr"/>
@@ -56161,7 +57401,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I541" t="inlineStr"/>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J541" t="inlineStr">
         <is>
           <t>1.6</t>
@@ -56371,7 +57615,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I543" t="inlineStr"/>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J543" t="inlineStr">
         <is>
           <t>1.07</t>
@@ -56474,7 +57722,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I544" t="inlineStr"/>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J544" t="inlineStr">
         <is>
           <t>0.3</t>
@@ -56577,7 +57829,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I545" t="inlineStr"/>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J545" t="inlineStr">
         <is>
           <t>2.85</t>
@@ -56783,7 +58039,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I547" t="inlineStr"/>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J547" t="inlineStr">
         <is>
           <t>0.24</t>
@@ -56989,7 +58249,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I549" t="inlineStr"/>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
       <c r="J549" t="inlineStr">
         <is>
           <t>2.12</t>
@@ -57092,7 +58356,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I550" t="inlineStr"/>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J550" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -57401,7 +58669,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I553" t="inlineStr"/>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J553" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -57710,7 +58982,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I556" t="inlineStr"/>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J556" t="inlineStr">
         <is>
           <t>1.35</t>
@@ -57813,7 +59089,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I557" t="inlineStr"/>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J557" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -57916,7 +59196,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I558" t="inlineStr"/>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J558" t="inlineStr">
         <is>
           <t>2.19</t>
@@ -58122,7 +59406,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I560" t="inlineStr"/>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J560" t="inlineStr">
         <is>
           <t>1.08</t>
@@ -58225,7 +59513,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I561" t="inlineStr"/>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J561" t="inlineStr">
         <is>
           <t>0.66</t>
@@ -58431,7 +59723,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I563" t="inlineStr"/>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J563" t="inlineStr">
         <is>
           <t>0.99</t>
@@ -58534,7 +59830,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr"/>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J564" t="inlineStr">
         <is>
           <t>2.81</t>
@@ -58740,7 +60040,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr"/>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J566" t="inlineStr">
         <is>
           <t>3.59</t>
@@ -58843,7 +60147,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I567" t="inlineStr"/>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J567" t="inlineStr">
         <is>
           <t>1.24</t>
@@ -59049,7 +60357,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I569" t="inlineStr"/>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J569" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -59358,7 +60670,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I572" t="inlineStr"/>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J572" t="inlineStr">
         <is>
           <t>3.16</t>
@@ -59461,7 +60777,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I573" t="inlineStr"/>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J573" t="inlineStr">
         <is>
           <t>0.76</t>
@@ -59770,7 +61090,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I576" t="inlineStr"/>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J576" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -59873,7 +61197,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I577" t="inlineStr"/>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J577" t="inlineStr">
         <is>
           <t>3.34</t>
@@ -59976,7 +61304,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I578" t="inlineStr"/>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J578" t="inlineStr">
         <is>
           <t>4.06</t>
@@ -60182,7 +61514,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I580" t="inlineStr"/>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J580" t="inlineStr">
         <is>
           <t>0.9</t>
@@ -60598,7 +61934,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I584" t="inlineStr"/>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J584" t="inlineStr">
         <is>
           <t>0.71</t>
@@ -60701,7 +62041,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I585" t="inlineStr"/>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J585" t="inlineStr">
         <is>
           <t>1.26</t>
@@ -60804,7 +62148,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I586" t="inlineStr"/>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J586" t="inlineStr">
         <is>
           <t>0.75</t>
@@ -60907,7 +62255,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I587" t="inlineStr"/>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J587" t="inlineStr">
         <is>
           <t>1.12</t>
@@ -61010,7 +62362,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I588" t="inlineStr"/>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J588" t="inlineStr">
         <is>
           <t>6.85</t>
@@ -61220,7 +62576,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I590" t="inlineStr"/>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J590" t="inlineStr">
         <is>
           <t>1.07</t>
@@ -61323,7 +62683,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I591" t="inlineStr"/>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J591" t="inlineStr">
         <is>
           <t>0.58</t>
@@ -61426,7 +62790,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I592" t="inlineStr"/>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J592" t="inlineStr">
         <is>
           <t>0.82</t>
@@ -61949,7 +63317,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I597" t="inlineStr"/>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J597" t="inlineStr">
         <is>
           <t>1.08</t>
@@ -62155,7 +63527,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I599" t="inlineStr"/>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J599" t="inlineStr">
         <is>
           <t>0.4</t>
@@ -62258,7 +63634,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I600" t="inlineStr"/>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J600" t="inlineStr">
         <is>
           <t>3.77</t>
@@ -62361,7 +63741,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I601" t="inlineStr"/>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J601" t="inlineStr">
         <is>
           <t>1.04</t>
@@ -62567,7 +63951,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I603" t="inlineStr"/>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J603" t="inlineStr">
         <is>
           <t>1.02</t>
@@ -62670,7 +64058,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I604" t="inlineStr"/>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J604" t="inlineStr">
         <is>
           <t>2.93</t>
@@ -62880,7 +64272,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I606" t="inlineStr"/>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J606" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -63086,7 +64482,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I608" t="inlineStr"/>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J608" t="inlineStr">
         <is>
           <t>0.96</t>
@@ -63189,7 +64589,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I609" t="inlineStr"/>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J609" t="inlineStr">
         <is>
           <t>6.09</t>
@@ -63395,7 +64799,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I611" t="inlineStr"/>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J611" t="inlineStr">
         <is>
           <t>0.42</t>
@@ -63498,7 +64906,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I612" t="inlineStr"/>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J612" t="inlineStr">
         <is>
           <t>0.41</t>
@@ -63807,7 +65219,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I615" t="inlineStr"/>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J615" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -63910,7 +65326,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I616" t="inlineStr"/>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J616" t="inlineStr">
         <is>
           <t>1.29</t>
@@ -64013,7 +65433,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I617" t="inlineStr"/>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J617" t="inlineStr">
         <is>
           <t>1.22</t>
@@ -64116,7 +65540,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I618" t="inlineStr"/>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J618" t="inlineStr">
         <is>
           <t>1.17</t>
@@ -64219,7 +65647,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I619" t="inlineStr"/>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J619" t="inlineStr">
         <is>
           <t>2.38</t>
@@ -64532,7 +65964,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I622" t="inlineStr"/>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J622" t="inlineStr">
         <is>
           <t>0.8</t>
@@ -64635,7 +66071,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I623" t="inlineStr"/>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J623" t="inlineStr">
         <is>
           <t>5.66</t>
@@ -64817,7 +66257,11 @@
       <c r="F625" t="inlineStr"/>
       <c r="G625" t="inlineStr"/>
       <c r="H625" t="inlineStr"/>
-      <c r="I625" t="inlineStr"/>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr"/>
@@ -65011,7 +66455,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I627" t="inlineStr"/>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J627" t="inlineStr">
         <is>
           <t>5.31</t>
@@ -65114,7 +66562,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I628" t="inlineStr"/>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J628" t="inlineStr">
         <is>
           <t>0.55</t>
@@ -65217,7 +66669,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I629" t="inlineStr"/>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J629" t="inlineStr">
         <is>
           <t>2.78</t>
@@ -65423,7 +66879,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I631" t="inlineStr"/>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J631" t="inlineStr">
         <is>
           <t>1.95</t>
@@ -65526,7 +66986,11 @@
           <t>55+</t>
         </is>
       </c>
-      <c r="I632" t="inlineStr"/>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J632" t="inlineStr">
         <is>
           <t>0.55</t>
@@ -65629,7 +67093,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I633" t="inlineStr"/>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J633" t="inlineStr">
         <is>
           <t>1.17</t>
@@ -65732,7 +67200,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I634" t="inlineStr"/>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J634" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -65835,7 +67307,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I635" t="inlineStr"/>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J635" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -66354,7 +67830,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I640" t="inlineStr"/>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J640" t="inlineStr">
         <is>
           <t>0.87</t>
@@ -66564,7 +68044,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I642" t="inlineStr"/>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J642" t="inlineStr">
         <is>
           <t>11.07</t>
@@ -67186,7 +68670,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I648" t="inlineStr"/>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J648" t="inlineStr">
         <is>
           <t>0.24</t>
@@ -67289,7 +68777,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I649" t="inlineStr"/>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
       <c r="J649" t="inlineStr">
         <is>
           <t>0.47</t>
@@ -67392,7 +68884,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I650" t="inlineStr"/>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J650" t="inlineStr">
         <is>
           <t>1.07</t>
@@ -67495,7 +68991,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I651" t="inlineStr"/>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J651" t="inlineStr">
         <is>
           <t>1.07</t>
@@ -67804,7 +69304,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I654" t="inlineStr"/>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J654" t="inlineStr">
         <is>
           <t>1.49</t>
@@ -67907,7 +69411,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I655" t="inlineStr"/>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J655" t="inlineStr">
         <is>
           <t>0.4</t>
@@ -68319,7 +69827,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I659" t="inlineStr"/>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J659" t="inlineStr">
         <is>
           <t>1.41</t>
@@ -68735,7 +70247,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I663" t="inlineStr"/>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J663" t="inlineStr">
         <is>
           <t>0.41</t>
@@ -68840,7 +70356,7 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
@@ -68945,7 +70461,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I665" t="inlineStr"/>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J665" t="inlineStr">
         <is>
           <t>1.01</t>
@@ -69048,7 +70568,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I666" t="inlineStr"/>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J666" t="inlineStr">
         <is>
           <t>1.37</t>
@@ -69151,7 +70675,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I667" t="inlineStr"/>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J667" t="inlineStr">
         <is>
           <t>2.04</t>
@@ -69357,7 +70885,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I669" t="inlineStr"/>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J669" t="inlineStr">
         <is>
           <t>0.11</t>
@@ -69460,7 +70992,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I670" t="inlineStr"/>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J670" t="inlineStr">
         <is>
           <t>0.88</t>
@@ -69666,7 +71202,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I672" t="inlineStr"/>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J672" t="inlineStr">
         <is>
           <t>0.46</t>
@@ -69872,7 +71412,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I674" t="inlineStr"/>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J674" t="inlineStr">
         <is>
           <t>0.64</t>
@@ -69975,7 +71519,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I675" t="inlineStr"/>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
       <c r="J675" t="inlineStr">
         <is>
           <t>0.78</t>
@@ -70284,7 +71832,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I678" t="inlineStr"/>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J678" t="inlineStr">
         <is>
           <t>0.34</t>
@@ -70387,7 +71939,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I679" t="inlineStr"/>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J679" t="inlineStr">
         <is>
           <t>3.13</t>
@@ -70593,7 +72149,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I681" t="inlineStr"/>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J681" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -70696,7 +72256,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I682" t="inlineStr"/>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J682" t="inlineStr">
         <is>
           <t>0.73</t>
@@ -70799,7 +72363,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I683" t="inlineStr"/>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J683" t="inlineStr">
         <is>
           <t>2.02</t>
@@ -71005,7 +72573,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I685" t="inlineStr"/>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J685" t="inlineStr">
         <is>
           <t>1.31</t>
@@ -71108,7 +72680,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I686" t="inlineStr"/>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J686" t="inlineStr">
         <is>
           <t>1.8</t>
@@ -71211,7 +72787,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I687" t="inlineStr"/>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J687" t="inlineStr">
         <is>
           <t>2.81</t>
@@ -71524,7 +73104,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I690" t="inlineStr"/>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J690" t="inlineStr">
         <is>
           <t>6.98</t>
@@ -71940,7 +73524,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I694" t="inlineStr"/>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J694" t="inlineStr">
         <is>
           <t>0.52</t>
@@ -72043,7 +73631,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I695" t="inlineStr"/>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J695" t="inlineStr">
         <is>
           <t>0.76</t>
@@ -72253,7 +73845,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I697" t="inlineStr"/>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J697" t="inlineStr">
         <is>
           <t>0.68</t>
@@ -72356,7 +73952,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I698" t="inlineStr"/>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J698" t="inlineStr">
         <is>
           <t>2.81</t>
@@ -72459,7 +74059,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I699" t="inlineStr"/>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J699" t="inlineStr">
         <is>
           <t>0.43</t>
@@ -72562,7 +74166,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I700" t="inlineStr"/>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J700" t="inlineStr">
         <is>
           <t>0.84</t>
@@ -72665,7 +74273,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I701" t="inlineStr"/>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J701" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -72768,7 +74380,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I702" t="inlineStr"/>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J702" t="inlineStr">
         <is>
           <t>1.41</t>
@@ -72871,7 +74487,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I703" t="inlineStr"/>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J703" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -72974,7 +74594,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I704" t="inlineStr"/>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J704" t="inlineStr">
         <is>
           <t>1.89</t>
@@ -73077,7 +74701,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I705" t="inlineStr"/>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J705" t="inlineStr">
         <is>
           <t>3.78</t>
@@ -73180,7 +74808,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I706" t="inlineStr"/>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J706" t="inlineStr">
         <is>
           <t>0.39</t>
@@ -73283,7 +74915,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I707" t="inlineStr"/>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J707" t="inlineStr">
         <is>
           <t>0.63</t>
@@ -73489,7 +75125,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I709" t="inlineStr"/>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J709" t="inlineStr">
         <is>
           <t>0.24</t>
@@ -73695,7 +75335,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I711" t="inlineStr"/>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J711" t="inlineStr">
         <is>
           <t>0.45</t>
@@ -73798,7 +75442,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I712" t="inlineStr"/>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J712" t="inlineStr">
         <is>
           <t>1.37</t>
@@ -74004,7 +75652,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I714" t="inlineStr"/>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J714" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -74107,7 +75759,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I715" t="inlineStr"/>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J715" t="inlineStr">
         <is>
           <t>0.32</t>
@@ -74210,7 +75866,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I716" t="inlineStr"/>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J716" t="inlineStr">
         <is>
           <t>1.32</t>
@@ -74313,7 +75973,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I717" t="inlineStr"/>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J717" t="inlineStr">
         <is>
           <t>0.91</t>
@@ -74416,7 +76080,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I718" t="inlineStr"/>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J718" t="inlineStr">
         <is>
           <t>3.63</t>
@@ -74622,7 +76290,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I720" t="inlineStr"/>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J720" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -74725,7 +76397,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I721" t="inlineStr"/>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J721" t="inlineStr">
         <is>
           <t>0.38</t>
@@ -75034,7 +76710,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I724" t="inlineStr"/>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J724" t="inlineStr">
         <is>
           <t>6.13</t>
@@ -75240,7 +76920,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I726" t="inlineStr"/>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J726" t="inlineStr">
         <is>
           <t>0.82</t>
@@ -75343,7 +77027,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I727" t="inlineStr"/>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J727" t="inlineStr">
         <is>
           <t>8.71</t>
@@ -75549,7 +77237,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I729" t="inlineStr"/>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J729" t="inlineStr">
         <is>
           <t>9.47</t>
@@ -75652,7 +77344,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I730" t="inlineStr"/>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J730" t="inlineStr">
         <is>
           <t>0.53</t>
@@ -75858,7 +77554,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I732" t="inlineStr"/>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J732" t="inlineStr">
         <is>
           <t>0.78</t>
@@ -75961,7 +77661,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I733" t="inlineStr"/>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J733" t="inlineStr">
         <is>
           <t>1.84</t>
@@ -76167,7 +77871,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I735" t="inlineStr"/>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J735" t="inlineStr">
         <is>
           <t>0.99</t>
@@ -76270,7 +77978,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I736" t="inlineStr"/>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J736" t="inlineStr">
         <is>
           <t>0.38</t>
@@ -76373,7 +78085,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I737" t="inlineStr"/>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J737" t="inlineStr">
         <is>
           <t>0.98</t>
@@ -76579,7 +78295,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I739" t="inlineStr"/>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J739" t="inlineStr">
         <is>
           <t>7.87</t>
@@ -76785,7 +78505,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I741" t="inlineStr"/>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J741" t="inlineStr">
         <is>
           <t>0.59</t>
@@ -76888,7 +78612,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I742" t="inlineStr"/>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J742" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -76991,7 +78719,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I743" t="inlineStr"/>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J743" t="inlineStr">
         <is>
           <t>0.73</t>
@@ -77094,7 +78826,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I744" t="inlineStr"/>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J744" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -77197,7 +78933,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I745" t="inlineStr"/>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J745" t="inlineStr">
         <is>
           <t>1.71</t>
@@ -77300,7 +79040,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I746" t="inlineStr"/>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J746" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -77716,7 +79460,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I750" t="inlineStr"/>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J750" t="inlineStr">
         <is>
           <t>0.76</t>
@@ -77819,7 +79567,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I751" t="inlineStr"/>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J751" t="inlineStr">
         <is>
           <t>1.64</t>
@@ -78025,7 +79777,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I753" t="inlineStr"/>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J753" t="inlineStr">
         <is>
           <t>0.39</t>
@@ -78231,7 +79987,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I755" t="inlineStr"/>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J755" t="inlineStr">
         <is>
           <t>0.79</t>
@@ -78437,7 +80197,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I757" t="inlineStr"/>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J757" t="inlineStr">
         <is>
           <t>0.8</t>
@@ -78540,7 +80304,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I758" t="inlineStr"/>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J758" t="inlineStr">
         <is>
           <t>0.21</t>
@@ -78643,7 +80411,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I759" t="inlineStr"/>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J759" t="inlineStr">
         <is>
           <t>11.59</t>
@@ -78849,7 +80621,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I761" t="inlineStr"/>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J761" t="inlineStr">
         <is>
           <t>0.24</t>
@@ -79055,7 +80831,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I763" t="inlineStr"/>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J763" t="inlineStr">
         <is>
           <t>2.15</t>
@@ -79158,7 +80938,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I764" t="inlineStr"/>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J764" t="inlineStr">
         <is>
           <t>0.42</t>
@@ -79261,7 +81045,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I765" t="inlineStr"/>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J765" t="inlineStr">
         <is>
           <t>1.05</t>
@@ -79340,7 +81128,11 @@
       <c r="F766" t="inlineStr"/>
       <c r="G766" t="inlineStr"/>
       <c r="H766" t="inlineStr"/>
-      <c r="I766" t="inlineStr"/>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J766" t="inlineStr"/>
       <c r="K766" t="inlineStr"/>
       <c r="L766" t="inlineStr"/>
@@ -79431,7 +81223,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I767" t="inlineStr"/>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J767" t="inlineStr">
         <is>
           <t>0.84</t>
@@ -79534,7 +81330,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I768" t="inlineStr"/>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J768" t="inlineStr">
         <is>
           <t>1.07</t>
@@ -79744,7 +81544,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I770" t="inlineStr"/>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J770" t="inlineStr">
         <is>
           <t>0.91</t>
@@ -80156,7 +81960,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I774" t="inlineStr"/>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J774" t="inlineStr">
         <is>
           <t>0.3</t>
@@ -80259,7 +82067,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I775" t="inlineStr"/>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J775" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -80362,7 +82174,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I776" t="inlineStr"/>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J776" t="inlineStr">
         <is>
           <t>2.13</t>
@@ -80568,7 +82384,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I778" t="inlineStr"/>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J778" t="inlineStr">
         <is>
           <t>1.25</t>
@@ -80881,7 +82701,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I781" t="inlineStr"/>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J781" t="inlineStr">
         <is>
           <t>1.53</t>
@@ -80984,7 +82808,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I782" t="inlineStr"/>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J782" t="inlineStr">
         <is>
           <t>5.02</t>
@@ -81087,7 +82915,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I783" t="inlineStr"/>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J783" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -81190,7 +83022,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I784" t="inlineStr"/>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J784" t="inlineStr">
         <is>
           <t>1.02</t>
@@ -81293,7 +83129,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I785" t="inlineStr"/>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J785" t="inlineStr">
         <is>
           <t>1.17</t>
@@ -81396,7 +83236,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I786" t="inlineStr"/>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J786" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -81602,7 +83446,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I788" t="inlineStr"/>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J788" t="inlineStr">
         <is>
           <t>8.75</t>
@@ -81911,7 +83759,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I791" t="inlineStr"/>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J791" t="inlineStr">
         <is>
           <t>0.47</t>
@@ -82224,7 +84076,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I794" t="inlineStr"/>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J794" t="inlineStr">
         <is>
           <t>15.44</t>
@@ -82327,7 +84183,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I795" t="inlineStr"/>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J795" t="inlineStr">
         <is>
           <t>0.28</t>
@@ -82430,7 +84290,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I796" t="inlineStr"/>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J796" t="inlineStr">
         <is>
           <t>3.76</t>
@@ -82533,7 +84397,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I797" t="inlineStr"/>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J797" t="inlineStr">
         <is>
           <t>0.26</t>
@@ -82636,7 +84504,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I798" t="inlineStr"/>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J798" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -82739,7 +84611,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I799" t="inlineStr"/>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J799" t="inlineStr">
         <is>
           <t>0.52</t>
@@ -82945,7 +84821,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I801" t="inlineStr"/>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J801" t="inlineStr">
         <is>
           <t>0.69</t>
@@ -83048,7 +84928,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I802" t="inlineStr"/>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J802" t="inlineStr">
         <is>
           <t>1.19</t>
@@ -83151,7 +85035,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I803" t="inlineStr"/>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J803" t="inlineStr">
         <is>
           <t>0.43</t>
@@ -83254,7 +85142,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I804" t="inlineStr"/>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J804" t="inlineStr">
         <is>
           <t>3.43</t>
@@ -83464,7 +85356,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I806" t="inlineStr"/>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J806" t="inlineStr">
         <is>
           <t>0.62</t>
@@ -83670,7 +85566,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I808" t="inlineStr"/>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J808" t="inlineStr">
         <is>
           <t>7.9</t>
@@ -83773,7 +85673,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I809" t="inlineStr"/>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J809" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -83876,7 +85780,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I810" t="inlineStr"/>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J810" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -83979,7 +85887,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I811" t="inlineStr"/>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J811" t="inlineStr">
         <is>
           <t>1.12</t>
@@ -84082,7 +85994,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I812" t="inlineStr"/>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J812" t="inlineStr">
         <is>
           <t>0.39</t>
@@ -84288,7 +86204,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I814" t="inlineStr"/>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J814" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -84391,7 +86311,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I815" t="inlineStr"/>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J815" t="inlineStr">
         <is>
           <t>0.26</t>
@@ -84597,7 +86521,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I817" t="inlineStr"/>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J817" t="inlineStr">
         <is>
           <t>1.02</t>
@@ -85009,7 +86937,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I821" t="inlineStr"/>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J821" t="inlineStr">
         <is>
           <t>0.37</t>
@@ -85112,7 +87044,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I822" t="inlineStr"/>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J822" t="inlineStr">
         <is>
           <t>0.49</t>
@@ -85215,7 +87151,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I823" t="inlineStr"/>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J823" t="inlineStr">
         <is>
           <t>0.56</t>
@@ -85318,7 +87258,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I824" t="inlineStr"/>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J824" t="inlineStr">
         <is>
           <t>0.51</t>
@@ -85524,7 +87468,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I826" t="inlineStr"/>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J826" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -85627,7 +87575,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I827" t="inlineStr"/>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J827" t="inlineStr">
         <is>
           <t>1.14</t>
@@ -85833,7 +87785,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I829" t="inlineStr"/>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J829" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -85936,7 +87892,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I830" t="inlineStr"/>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J830" t="inlineStr">
         <is>
           <t>0.53</t>
@@ -86039,7 +87999,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I831" t="inlineStr"/>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J831" t="inlineStr">
         <is>
           <t>1.24</t>
@@ -86245,7 +88209,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I833" t="inlineStr"/>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J833" t="inlineStr">
         <is>
           <t>0.52</t>
@@ -86348,7 +88316,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I834" t="inlineStr"/>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J834" t="inlineStr">
         <is>
           <t>0.82</t>
@@ -86451,7 +88423,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I835" t="inlineStr"/>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J835" t="inlineStr">
         <is>
           <t>0.69</t>
@@ -86554,7 +88530,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I836" t="inlineStr"/>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J836" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -86760,7 +88740,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I838" t="inlineStr"/>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
       <c r="J838" t="inlineStr">
         <is>
           <t>0.32</t>
@@ -86863,7 +88847,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I839" t="inlineStr"/>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J839" t="inlineStr">
         <is>
           <t>0.97</t>
@@ -86966,7 +88954,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I840" t="inlineStr"/>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J840" t="inlineStr">
         <is>
           <t>0.63</t>
@@ -87069,7 +89061,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I841" t="inlineStr"/>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J841" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -87277,7 +89273,7 @@
       </c>
       <c r="I843" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="J843" t="inlineStr">
@@ -87382,7 +89378,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I844" t="inlineStr"/>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J844" t="inlineStr">
         <is>
           <t>3.78</t>
@@ -87901,7 +89901,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I849" t="inlineStr"/>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J849" t="inlineStr">
         <is>
           <t>0.72</t>
@@ -88004,7 +90008,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I850" t="inlineStr"/>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J850" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -88107,7 +90115,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I851" t="inlineStr"/>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J851" t="inlineStr">
         <is>
           <t>1.04</t>
@@ -88317,7 +90329,11 @@
           <t>45-54</t>
         </is>
       </c>
-      <c r="I853" t="inlineStr"/>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J853" t="inlineStr">
         <is>
           <t>0.23</t>
@@ -88420,7 +90436,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I854" t="inlineStr"/>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J854" t="inlineStr">
         <is>
           <t>0.86</t>
@@ -88523,7 +90543,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I855" t="inlineStr"/>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
       <c r="J855" t="inlineStr">
         <is>
           <t>1.65</t>
@@ -88626,7 +90650,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I856" t="inlineStr"/>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J856" t="inlineStr">
         <is>
           <t>1.01</t>
@@ -88729,7 +90757,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I857" t="inlineStr"/>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J857" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -88832,7 +90864,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I858" t="inlineStr"/>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J858" t="inlineStr">
         <is>
           <t>1.32</t>
@@ -88935,7 +90971,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I859" t="inlineStr"/>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J859" t="inlineStr">
         <is>
           <t>0.94</t>
@@ -89141,7 +91181,11 @@
           <t>18-24</t>
         </is>
       </c>
-      <c r="I861" t="inlineStr"/>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J861" t="inlineStr">
         <is>
           <t>0.93</t>
@@ -89349,7 +91393,7 @@
       </c>
       <c r="I863" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="J863" t="inlineStr">
@@ -89454,7 +91498,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I864" t="inlineStr"/>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J864" t="inlineStr">
         <is>
           <t>2.33</t>
@@ -89557,7 +91605,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I865" t="inlineStr"/>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>East/SE Asian</t>
+        </is>
+      </c>
       <c r="J865" t="inlineStr">
         <is>
           <t>0.56</t>
@@ -89660,7 +91712,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I866" t="inlineStr"/>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J866" t="inlineStr">
         <is>
           <t>1.13</t>
@@ -90076,7 +92132,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I870" t="inlineStr"/>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J870" t="inlineStr">
         <is>
           <t>0.8</t>
@@ -90179,7 +92239,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I871" t="inlineStr"/>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
       <c r="J871" t="inlineStr">
         <is>
           <t>0.71</t>
@@ -90282,7 +92346,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I872" t="inlineStr"/>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J872" t="inlineStr">
         <is>
           <t>0.64</t>
@@ -90488,7 +92556,11 @@
           <t>25-34</t>
         </is>
       </c>
-      <c r="I874" t="inlineStr"/>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
       <c r="J874" t="inlineStr">
         <is>
           <t>0.5</t>
@@ -90694,7 +92766,11 @@
           <t>35-44</t>
         </is>
       </c>
-      <c r="I876" t="inlineStr"/>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
       <c r="J876" t="inlineStr">
         <is>
           <t>0.75</t>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -625,10 +625,10 @@
         <v>46088.58265046297</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46169.47780092592</v>
+        <v>46253.39663194444</v>
       </c>
       <c r="R2" t="n">
-        <v>35.9</v>
+        <v>41.8</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Spearmint, Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other, Spearmint, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4651,7 +4651,7 @@
         <v>46103.6757175926</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46238.49519675926</v>
+        <v>46253.41400462963</v>
       </c>
       <c r="R40" t="n">
         <v>46</v>
@@ -13792,11 +13792,11 @@
         </is>
       </c>
       <c r="M127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -13808,7 +13808,7 @@
         <v>46132.27987268518</v>
       </c>
       <c r="Q127" s="1" t="n">
-        <v>46252.74871527778</v>
+        <v>46253.83552083333</v>
       </c>
       <c r="R127" t="n">
         <v>29.1</v>
@@ -17505,7 +17505,7 @@
         </is>
       </c>
       <c r="M162" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
@@ -17521,10 +17521,10 @@
         <v>46113.59237268518</v>
       </c>
       <c r="Q162" s="1" t="n">
-        <v>46247.35839120371</v>
+        <v>46253.42024305555</v>
       </c>
       <c r="R162" t="n">
-        <v>39.5</v>
+        <v>45.5</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="M173" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -18686,10 +18686,10 @@
         <v>45992.76762731482</v>
       </c>
       <c r="Q173" s="1" t="n">
-        <v>46248.55422453704</v>
+        <v>46253.43552083334</v>
       </c>
       <c r="R173" t="n">
-        <v>93.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         </is>
       </c>
       <c r="M230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -24657,10 +24657,10 @@
         <v>45946.90708333333</v>
       </c>
       <c r="Q230" s="1" t="n">
-        <v>46220.4459375</v>
+        <v>46253.42163194445</v>
       </c>
       <c r="R230" t="n">
-        <v>27</v>
+        <v>38.9</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -27704,26 +27704,26 @@
         </is>
       </c>
       <c r="M259" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Green Burner</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P259" s="1" t="n">
         <v>46097.51252314815</v>
       </c>
       <c r="Q259" s="1" t="n">
-        <v>46247.35841435185</v>
+        <v>46253.78621527777</v>
       </c>
       <c r="R259" t="n">
-        <v>12</v>
+        <v>23.9</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         </is>
       </c>
       <c r="M348" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N348" t="inlineStr">
         <is>
@@ -37079,10 +37079,10 @@
         <v>46063.34931712963</v>
       </c>
       <c r="Q348" s="1" t="n">
-        <v>46248.94450231481</v>
+        <v>46253.40774305556</v>
       </c>
       <c r="R348" t="n">
-        <v>54.4</v>
+        <v>60.4</v>
       </c>
       <c r="S348" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         </is>
       </c>
       <c r="M370" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N370" t="inlineStr">
         <is>
@@ -39409,10 +39409,10 @@
         <v>46084.40070601852</v>
       </c>
       <c r="Q370" s="1" t="n">
-        <v>46249.63340277778</v>
+        <v>46253.42163194445</v>
       </c>
       <c r="R370" t="n">
-        <v>38</v>
+        <v>43.9</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         </is>
       </c>
       <c r="M506" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N506" t="inlineStr">
         <is>
@@ -53733,10 +53733,10 @@
         <v>46167.56946759259</v>
       </c>
       <c r="Q506" s="1" t="n">
-        <v>46203.53965277778</v>
+        <v>46253.43972222223</v>
       </c>
       <c r="R506" t="n">
-        <v>17.9</v>
+        <v>23.9</v>
       </c>
       <c r="S506" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         </is>
       </c>
       <c r="M543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N543" t="inlineStr">
         <is>
@@ -57649,17 +57649,17 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P543" s="1" t="n">
         <v>46196.57509259259</v>
       </c>
       <c r="Q543" s="1" t="n">
-        <v>46226.46194444445</v>
+        <v>46253.49040509259</v>
       </c>
       <c r="R543" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S543" t="inlineStr">
         <is>
@@ -60235,11 +60235,11 @@
         </is>
       </c>
       <c r="M568" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Other</t>
+          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other</t>
         </is>
       </c>
       <c r="O568" t="inlineStr">
@@ -60251,10 +60251,10 @@
         <v>46104.48613425926</v>
       </c>
       <c r="Q568" s="1" t="n">
-        <v>46245.41951388889</v>
+        <v>46253.43760416667</v>
       </c>
       <c r="R568" t="n">
-        <v>29.9</v>
+        <v>34.6</v>
       </c>
       <c r="S568" t="inlineStr">
         <is>
@@ -69832,26 +69832,26 @@
         </is>
       </c>
       <c r="M659" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Hibiscus</t>
         </is>
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P659" s="1" t="n">
         <v>46196.5750462963</v>
       </c>
       <c r="Q659" s="1" t="n">
-        <v>46230.53484953703</v>
+        <v>46253.42372685186</v>
       </c>
       <c r="R659" t="n">
-        <v>12</v>
+        <v>16.7</v>
       </c>
       <c r="S659" t="inlineStr">
         <is>
@@ -87798,7 +87798,7 @@
         </is>
       </c>
       <c r="M829" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N829" t="inlineStr">
         <is>
@@ -87814,10 +87814,10 @@
         <v>46103.68543981481</v>
       </c>
       <c r="Q829" s="1" t="n">
-        <v>46249.69866898148</v>
+        <v>46253.4105324074</v>
       </c>
       <c r="R829" t="n">
-        <v>17.9</v>
+        <v>23.8</v>
       </c>
       <c r="S829" t="inlineStr">
         <is>
@@ -89914,11 +89914,11 @@
         </is>
       </c>
       <c r="M849" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N849" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O849" t="inlineStr">
@@ -89930,7 +89930,7 @@
         <v>45911.18621527778</v>
       </c>
       <c r="Q849" s="1" t="n">
-        <v>46181.47432870371</v>
+        <v>46253.67996527778</v>
       </c>
       <c r="R849" t="n">
         <v>11.9</v>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -88460,26 +88460,26 @@
         </is>
       </c>
       <c r="M831" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N831" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O831" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P831" s="1" t="n">
         <v>46176.59101851852</v>
       </c>
       <c r="Q831" s="1" t="n">
-        <v>46176.59101851852</v>
+        <v>46258.77788194444</v>
       </c>
       <c r="R831" t="n">
-        <v>6</v>
+        <v>17.9</v>
       </c>
       <c r="S831" t="inlineStr">
         <is>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -1144,11 +1144,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Hibiscus, Other, Spearmint</t>
+          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other, Spearmint, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1160,10 +1160,10 @@
         <v>46084.40070601852</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46252.72302083333</v>
+        <v>46259.07788194445</v>
       </c>
       <c r="R7" t="n">
-        <v>15.6</v>
+        <v>40</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -5868,10 +5868,10 @@
         <v>45915.34108796297</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46238.34313657408</v>
+        <v>46259.59388888889</v>
       </c>
       <c r="R51" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -6610,17 +6610,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P58" s="1" t="n">
         <v>46217.30975694444</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46217.30975694444</v>
+        <v>46259.61329861111</v>
       </c>
       <c r="R58" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10025,26 +10025,26 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Ashwagandha, Ashwagandha Coffee, Green Burner, Turmeric Curcumin</t>
+          <t>Ashwagandha, Ashwagandha Coffee, Green Burner, Hibiscus, Other, Spearmint, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P90" s="1" t="n">
         <v>45925.5902199074</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46062.76112268519</v>
+        <v>46259.37581018519</v>
       </c>
       <c r="R90" t="n">
-        <v>27.3</v>
+        <v>48.9</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>TikTok Shop (FBT)</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P121" s="1" t="n">
@@ -13357,7 +13357,7 @@
         <v>46261.97024305556</v>
       </c>
       <c r="R121" t="n">
-        <v>17.9</v>
+        <v>23.9</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -82356,26 +82356,26 @@
         </is>
       </c>
       <c r="M767" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N767" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Green Burner</t>
         </is>
       </c>
       <c r="O767" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TikTok Shop (FBT), seller</t>
         </is>
       </c>
       <c r="P767" s="1" t="n">
         <v>46251.29798611111</v>
       </c>
       <c r="Q767" s="1" t="n">
-        <v>46251.29798611111</v>
+        <v>46259.87857638889</v>
       </c>
       <c r="R767" t="n">
-        <v>6</v>
+        <v>11.9</v>
       </c>
       <c r="S767" t="inlineStr">
         <is>
@@ -85138,11 +85138,11 @@
         </is>
       </c>
       <c r="M793" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N793" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Spearmint</t>
+          <t>Ashwagandha Coffee, Green Burner, Other, Spearmint</t>
         </is>
       </c>
       <c r="O793" t="inlineStr">
@@ -85154,10 +85154,10 @@
         <v>46197.65899305556</v>
       </c>
       <c r="Q793" s="1" t="n">
-        <v>46245.343125</v>
+        <v>46259.49107638889</v>
       </c>
       <c r="R793" t="n">
-        <v>16.9</v>
+        <v>22.8</v>
       </c>
       <c r="S793" t="inlineStr">
         <is>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -25017,16 +25017,52 @@
           <t>https://www.tiktok.com/@zimchi_meal</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>81179</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>100K-250K</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>142535</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Kitchenware, Household Appliances, Luggage &amp; Bags</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>94.88</t>
+        </is>
+      </c>
       <c r="M231" t="n">
         <v>2</v>
       </c>
@@ -37269,7 +37305,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -37279,7 +37315,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -37299,12 +37335,12 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Health, Sports &amp; Outdoor, Food &amp; Beverages</t>
+          <t>Health, Sports &amp; Outdoor, Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -40800,7 +40836,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -40810,7 +40846,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -40820,7 +40856,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -40830,17 +40866,17 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Household Appliances, Shoes, Health</t>
+          <t>Health, Household Appliances, Kitchenware</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>95.38</t>
+          <t>95.53</t>
         </is>
       </c>
       <c r="M379" t="n">

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
         <v>45975.49006944444</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46133.44170138889</v>
+        <v>46274.39523148148</v>
       </c>
       <c r="R28" t="n">
-        <v>36.4</v>
+        <v>42.4</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -8511,10 +8511,10 @@
         <v>46153.38871527778</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46174.3319675926</v>
+        <v>46274.56113425926</v>
       </c>
       <c r="R76" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -49470,11 +49470,11 @@
         </is>
       </c>
       <c r="M461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Green Burner</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -49486,10 +49486,10 @@
         <v>46217.45280092592</v>
       </c>
       <c r="Q461" s="1" t="n">
-        <v>46217.45280092592</v>
+        <v>46274.39519675926</v>
       </c>
       <c r="R461" t="n">
-        <v>6</v>
+        <v>11.9</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
